--- a/data/trans_camb/P16A11-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 5,21</t>
+          <t>-6,0; 5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 3,41</t>
+          <t>-7,47; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,05</t>
+          <t>1,75; 13,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,13</t>
+          <t>-5,52; 7,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 4,04</t>
+          <t>-8,15; 3,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 8,81</t>
+          <t>-1,13; 9,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,57</t>
+          <t>-3,73; 4,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,87</t>
+          <t>-6,16; 1,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,37</t>
+          <t>1,14; 9,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 53,04</t>
+          <t>-40,61; 55,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 38,58</t>
+          <t>-51,92; 32,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 135,35</t>
+          <t>10,76; 134,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 61,1</t>
+          <t>-31,26; 63,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 35,22</t>
+          <t>-46,45; 33,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 76,08</t>
+          <t>-6,84; 83,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 38,91</t>
+          <t>-24,48; 42,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 17,64</t>
+          <t>-39,15; 19,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 80,0</t>
+          <t>7,19; 82,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,55</t>
+          <t>0,82; 9,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,29</t>
+          <t>1,19; 10,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,27</t>
+          <t>0,38; 8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 7,51</t>
+          <t>-2,02; 8,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,15</t>
+          <t>-0,46; 10,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 1,41</t>
+          <t>-7,18; 1,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,32</t>
+          <t>0,31; 6,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,36</t>
+          <t>1,71; 8,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,67</t>
+          <t>-2,32; 3,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 111,67</t>
+          <t>6,01; 116,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 110,59</t>
+          <t>6,56; 113,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 98,26</t>
+          <t>1,55; 95,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 48,15</t>
+          <t>-10,68; 56,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 64,66</t>
+          <t>-2,21; 65,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 9,45</t>
+          <t>-35,24; 8,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 56,75</t>
+          <t>2,05; 55,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 66,35</t>
+          <t>10,75; 67,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 29,19</t>
+          <t>-14,76; 30,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 10,6</t>
+          <t>-0,78; 10,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,39</t>
+          <t>-3,98; 6,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,43</t>
+          <t>2,46; 13,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,43</t>
+          <t>-2,72; 9,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 1,71</t>
+          <t>-9,88; 1,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 9,74</t>
+          <t>-0,59; 10,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,45</t>
+          <t>-0,09; 8,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,5</t>
+          <t>-4,81; 3,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,61</t>
+          <t>1,88; 9,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 90,85</t>
+          <t>-4,52; 105,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 66,49</t>
+          <t>-23,8; 62,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 116,69</t>
+          <t>14,2; 122,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 55,01</t>
+          <t>-12,14; 61,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 10,34</t>
+          <t>-44,34; 10,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 59,89</t>
+          <t>-2,98; 62,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 59,39</t>
+          <t>-0,84; 55,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 17,67</t>
+          <t>-26,16; 20,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 73,42</t>
+          <t>9,68; 66,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,39</t>
+          <t>-0,35; 10,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 9,12</t>
+          <t>-1,63; 8,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 12,75</t>
+          <t>0,78; 12,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,89</t>
+          <t>0,73; 12,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,78</t>
+          <t>-2,5; 9,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 4,98</t>
+          <t>-8,69; 5,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,69</t>
+          <t>1,7; 9,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,5</t>
+          <t>-0,43; 7,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,76</t>
+          <t>-3,42; 6,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 92,43</t>
+          <t>-2,27; 92,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 82,08</t>
+          <t>-9,9; 75,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 107,79</t>
+          <t>4,59; 109,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 84,27</t>
+          <t>2,58; 83,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 57,25</t>
+          <t>-11,75; 58,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 29,73</t>
+          <t>-42,73; 32,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 69,96</t>
+          <t>9,56; 71,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 52,48</t>
+          <t>-2,77; 54,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 48,57</t>
+          <t>-17,69; 47,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 13,16</t>
+          <t>0,67; 13,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,09</t>
+          <t>-3,55; 7,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 16,25</t>
+          <t>4,32; 16,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 21,54</t>
+          <t>6,45; 22,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 14,44</t>
+          <t>0,47; 14,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,32; 20,24</t>
+          <t>8,25; 20,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 15,61</t>
+          <t>5,81; 15,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,07</t>
+          <t>0,58; 9,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 16,5</t>
+          <t>8,69; 17,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,74; 208,7</t>
+          <t>3,83; 227,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 119,56</t>
+          <t>-34,67; 127,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37,35; 265,33</t>
+          <t>34,33; 280,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39,93; 253,77</t>
+          <t>40,17; 263,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 165,63</t>
+          <t>2,12; 169,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,26; 245,59</t>
+          <t>50,11; 250,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,93; 184,02</t>
+          <t>43,43; 184,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 105,03</t>
+          <t>3,95; 111,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>61,73; 209,06</t>
+          <t>66,05; 216,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,81; 14,47</t>
+          <t>0,12; 13,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,95</t>
+          <t>-8,31; 3,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,08; 18,35</t>
+          <t>6,21; 18,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 10,27</t>
+          <t>-3,97; 10,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 4,0</t>
+          <t>-9,63; 3,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 10,28</t>
+          <t>-1,8; 10,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,37</t>
+          <t>0,43; 9,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 1,6</t>
+          <t>-6,5; 2,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,03</t>
+          <t>3,63; 12,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,58; 112,8</t>
+          <t>0,13; 109,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 31,16</t>
+          <t>-43,04; 31,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31,25; 150,41</t>
+          <t>31,87; 159,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 66,89</t>
+          <t>-17,07; 64,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 26,64</t>
+          <t>-42,22; 26,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 67,25</t>
+          <t>-8,96; 65,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,66; 70,77</t>
+          <t>2,37; 66,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 10,93</t>
+          <t>-33,26; 13,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,33; 79,87</t>
+          <t>17,65; 84,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 8,45</t>
+          <t>-0,14; 8,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,66</t>
+          <t>-3,87; 4,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 7,51</t>
+          <t>-0,8; 7,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 8,73</t>
+          <t>-0,1; 8,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -0,53</t>
+          <t>-8,23; -0,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 49,08</t>
+          <t>-0,38; 51,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,92</t>
+          <t>1,09; 7,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,82</t>
+          <t>-4,93; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,23; 40,57</t>
+          <t>1,07; 38,01</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 68,65</t>
+          <t>-1,39; 63,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 38,68</t>
+          <t>-23,89; 32,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 59,65</t>
+          <t>-5,41; 59,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 52,37</t>
+          <t>-0,72; 50,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,69; -3,09</t>
+          <t>-40,67; -1,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 325,06</t>
+          <t>-2,32; 324,01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,02; 45,24</t>
+          <t>5,98; 46,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 5,17</t>
+          <t>-28,03; 4,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,45; 255,56</t>
+          <t>6,01; 235,75</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,81</t>
+          <t>-1,03; 5,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,17</t>
+          <t>0,91; 7,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 7,99</t>
+          <t>-7,3; 7,83</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,83</t>
+          <t>-0,34; 6,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,13</t>
+          <t>1,47; 9,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,59; 12,69</t>
+          <t>5,38; 12,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,43</t>
+          <t>0,44; 5,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,4</t>
+          <t>2,43; 7,62</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 8,56</t>
+          <t>-2,47; 8,66</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 58,07</t>
+          <t>-8,24; 56,35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,43; 81,97</t>
+          <t>5,89; 76,11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 72,39</t>
+          <t>-50,54; 70,98</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 58,26</t>
+          <t>-2,31; 62,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,3; 77,72</t>
+          <t>9,48; 83,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,94; 113,66</t>
+          <t>34,8; 115,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,62; 46,04</t>
+          <t>3,21; 46,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>16,44; 65,24</t>
+          <t>17,97; 66,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 70,54</t>
+          <t>-16,78; 72,57</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,78</t>
+          <t>2,4; 5,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,95</t>
+          <t>0,6; 3,95</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,31</t>
+          <t>1,29; 7,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,17</t>
+          <t>2,32; 6,05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,84</t>
+          <t>-0,78; 2,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,9; 22,26</t>
+          <t>2,81; 20,6</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,4</t>
+          <t>2,89; 5,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,99</t>
+          <t>0,35; 2,84</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,42</t>
+          <t>3,64; 16,87</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>16,44; 48,97</t>
+          <t>17,27; 48,24</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4,64; 33,87</t>
+          <t>4,52; 33,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,22; 60,54</t>
+          <t>11,63; 58,49</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,19; 39,59</t>
+          <t>13,53; 38,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 18,31</t>
+          <t>-4,44; 18,79</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,27; 129,5</t>
+          <t>16,33; 128,3</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,31</t>
+          <t>18,72; 39,13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,54; 21,34</t>
+          <t>2,43; 20,28</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24,12; 103,79</t>
+          <t>24,26; 116,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A11-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,49</t>
+          <t>-6,06; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 3,22</t>
+          <t>-6,82; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 13,25</t>
+          <t>2,65; 14,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,17</t>
+          <t>-5,13; 6,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,69</t>
+          <t>-8,24; 4,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,11</t>
+          <t>-3,18; 7,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,64</t>
+          <t>-3,67; 4,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 1,93</t>
+          <t>-6,03; 2,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,24</t>
+          <t>1,72; 9,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 55,4</t>
+          <t>-41,11; 53,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 32,68</t>
+          <t>-47,53; 34,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 134,24</t>
+          <t>16,19; 148,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 63,78</t>
+          <t>-28,38; 60,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 33,58</t>
+          <t>-45,22; 32,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 83,26</t>
+          <t>-17,26; 67,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 42,77</t>
+          <t>-24,15; 40,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 19,16</t>
+          <t>-40,57; 17,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 82,83</t>
+          <t>10,77; 82,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,63</t>
+          <t>0,71; 9,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,01</t>
+          <t>0,7; 9,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,64</t>
+          <t>-0,26; 8,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 8,37</t>
+          <t>-2,22; 7,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 10,0</t>
+          <t>-0,49; 10,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,27</t>
+          <t>-6,97; 1,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,99</t>
+          <t>0,68; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,36</t>
+          <t>1,89; 8,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,99</t>
+          <t>-2,6; 3,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,03%</t>
+          <t>-15,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 116,45</t>
+          <t>5,48; 112,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 113,0</t>
+          <t>4,8; 111,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 95,6</t>
+          <t>-3,68; 97,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 56,06</t>
+          <t>-11,27; 47,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 65,68</t>
+          <t>-2,57; 67,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 8,55</t>
+          <t>-33,87; 9,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 55,36</t>
+          <t>4,33; 58,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 67,46</t>
+          <t>11,83; 68,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 30,77</t>
+          <t>-15,86; 26,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 10,85</t>
+          <t>-1,25; 10,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 6,84</t>
+          <t>-3,97; 6,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,48</t>
+          <t>2,42; 13,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 9,92</t>
+          <t>-3,53; 9,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 1,74</t>
+          <t>-10,23; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 10,43</t>
+          <t>-1,75; 9,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 8,47</t>
+          <t>-0,3; 8,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,16</t>
+          <t>-5,61; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,96</t>
+          <t>1,57; 9,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 105,39</t>
+          <t>-7,48; 95,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 62,02</t>
+          <t>-24,81; 64,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 122,65</t>
+          <t>12,31; 120,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 61,12</t>
+          <t>-16,92; 55,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 10,27</t>
+          <t>-44,63; 14,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 62,91</t>
+          <t>-7,62; 53,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 55,5</t>
+          <t>-2,07; 56,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 20,85</t>
+          <t>-29,54; 17,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 66,95</t>
+          <t>8,6; 67,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,08</t>
+          <t>-0,63; 10,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 8,39</t>
+          <t>-1,13; 9,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 12,29</t>
+          <t>-0,17; 10,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 12,68</t>
+          <t>0,79; 12,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 9,14</t>
+          <t>-2,49; 9,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 5,2</t>
+          <t>-2,89; 7,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,99</t>
+          <t>1,49; 9,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,86</t>
+          <t>-0,51; 7,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,92</t>
+          <t>0,78; 8,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,49%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 92,69</t>
+          <t>-4,56; 99,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 75,69</t>
+          <t>-7,91; 82,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 109,56</t>
+          <t>-0,15; 98,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 83,54</t>
+          <t>3,89; 80,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 58,54</t>
+          <t>-12,19; 58,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 32,22</t>
+          <t>-13,35; 46,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,56; 71,2</t>
+          <t>8,28; 70,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 54,12</t>
+          <t>-2,36; 53,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 47,44</t>
+          <t>4,23; 60,7</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>8,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>13,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,67</t>
+          <t>11,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 13,46</t>
+          <t>0,3; 13,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,79</t>
+          <t>-3,13; 8,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,48</t>
+          <t>2,48; 14,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 22,78</t>
+          <t>7,06; 21,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 14,54</t>
+          <t>0,46; 14,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 20,21</t>
+          <t>7,22; 18,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,84</t>
+          <t>5,55; 14,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 9,38</t>
+          <t>0,11; 9,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,69; 17,04</t>
+          <t>6,75; 15,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116,48%</t>
+          <t>100,48%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>121,06%</t>
+          <t>110,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>121,5%</t>
+          <t>107,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,83; 227,84</t>
+          <t>1,24; 219,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 127,24</t>
+          <t>-29,3; 142,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34,33; 280,26</t>
+          <t>18,7; 243,02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40,17; 263,5</t>
+          <t>41,85; 253,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,12; 169,98</t>
+          <t>3,07; 180,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,11; 250,98</t>
+          <t>42,16; 224,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,43; 184,17</t>
+          <t>44,78; 183,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,95; 111,74</t>
+          <t>1,06; 113,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>66,05; 216,58</t>
+          <t>50,54; 202,47</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11,83</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>7,85</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,12; 13,77</t>
+          <t>0,67; 14,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 3,81</t>
+          <t>-8,22; 3,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,21; 18,1</t>
+          <t>4,78; 17,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,17</t>
+          <t>-3,1; 10,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 3,65</t>
+          <t>-8,94; 4,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 10,28</t>
+          <t>-2,42; 9,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,93</t>
+          <t>0,52; 10,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 2,12</t>
+          <t>-6,92; 2,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,63; 12,41</t>
+          <t>3,86; 12,31</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,13; 109,52</t>
+          <t>2,01; 111,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 31,86</t>
+          <t>-43,91; 30,27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31,87; 159,38</t>
+          <t>24,26; 144,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 64,03</t>
+          <t>-14,27; 68,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 26,73</t>
+          <t>-40,73; 23,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 65,84</t>
+          <t>-10,23; 61,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,37; 66,64</t>
+          <t>2,12; 65,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 13,61</t>
+          <t>-34,49; 12,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,65; 84,69</t>
+          <t>18,88; 81,34</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,32</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>2,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,2</t>
+          <t>-0,44; 8,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 4,17</t>
+          <t>-3,69; 4,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,39</t>
+          <t>-0,24; 7,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,53</t>
+          <t>-0,1; 8,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -0,21</t>
+          <t>-8,58; -0,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 51,26</t>
+          <t>-1,9; 6,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,03</t>
+          <t>1,13; 7,13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,66</t>
+          <t>-4,95; 0,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 38,01</t>
+          <t>-0,07; 5,65</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>109,35%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 63,46</t>
+          <t>-3,02; 65,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 32,57</t>
+          <t>-21,38; 33,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 59,01</t>
+          <t>-1,51; 62,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 50,61</t>
+          <t>-0,02; 56,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,67; -1,72</t>
+          <t>-41,41; -1,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 324,01</t>
+          <t>-9,21; 39,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,98; 46,89</t>
+          <t>5,55; 46,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 4,16</t>
+          <t>-27,15; 6,4</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,01; 235,75</t>
+          <t>-0,77; 37,38</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,92</t>
+          <t>-1,22; 5,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,89</t>
+          <t>0,87; 7,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 7,83</t>
+          <t>2,22; 9,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,99</t>
+          <t>-0,25; 7,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 9,29</t>
+          <t>1,34; 9,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,92</t>
+          <t>4,57; 11,28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,28</t>
+          <t>0,28; 5,31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,62</t>
+          <t>2,18; 7,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,66</t>
+          <t>4,51; 9,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 56,35</t>
+          <t>-7,86; 58,73</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,89; 76,11</t>
+          <t>5,73; 79,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 70,98</t>
+          <t>15,58; 90,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 62,14</t>
+          <t>-1,8; 61,55</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,48; 83,15</t>
+          <t>9,06; 82,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,8; 115,47</t>
+          <t>28,19; 98,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,21; 46,96</t>
+          <t>1,66; 46,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,97; 66,72</t>
+          <t>15,83; 67,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 72,57</t>
+          <t>31,41; 83,8</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,79</t>
+          <t>2,32; 5,72</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,95</t>
+          <t>0,48; 3,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,11</t>
+          <t>4,5; 7,94</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,05</t>
+          <t>2,29; 6,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,94</t>
+          <t>-0,86; 2,9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,81; 20,6</t>
+          <t>2,37; 5,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,53</t>
+          <t>2,83; 5,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,84</t>
+          <t>0,34; 2,99</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,87</t>
+          <t>3,76; 6,2</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,27; 48,24</t>
+          <t>16,86; 48,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4,52; 33,01</t>
+          <t>3,62; 31,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>11,63; 58,49</t>
+          <t>32,88; 66,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,53; 38,73</t>
+          <t>12,75; 38,66</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 18,79</t>
+          <t>-4,96; 18,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,33; 128,3</t>
+          <t>13,31; 34,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,72; 39,13</t>
+          <t>18,51; 38,89</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,28</t>
+          <t>2,18; 21,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24,26; 116,96</t>
+          <t>24,8; 44,47</t>
         </is>
       </c>
     </row>
